--- a/Result/profitability/6574.xlsx
+++ b/Result/profitability/6574.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM46"/>
+  <dimension ref="A1:AM47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6272,6 +6272,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>6574</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>219</v>
+      </c>
+      <c r="D47" t="n">
+        <v>101</v>
+      </c>
+      <c r="E47" t="n">
+        <v>118</v>
+      </c>
+      <c r="F47" t="n">
+        <v>53.84</v>
+      </c>
+      <c r="G47" t="n">
+        <v>86</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>39.05%</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>62</v>
+      </c>
+      <c r="J47" t="n">
+        <v>147</v>
+      </c>
+      <c r="K47" t="n">
+        <v>127</v>
+      </c>
+      <c r="L47" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.3525</v>
+      </c>
+      <c r="N47" t="n">
+        <v>60.70625</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
+      </c>
+      <c r="V47" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.756838905775076</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>-3.529999999999994</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>-0.06153041659403857</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>3.378787878787879</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>-10.75999999999999</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>-0.1665634674922599</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK47" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
